--- a/Documentation/Best For Lists/Best for Seniors with Dementia List.xlsx
+++ b/Documentation/Best For Lists/Best for Seniors with Dementia List.xlsx
@@ -82,7 +82,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00999999"/>
-      <sz val="12"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -195,10 +195,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -591,15 +591,15 @@
   <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
@@ -607,7 +607,7 @@
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -620,49 +620,49 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-27  |  Filter: one product per Manufacturer × Price Category × Animal Category  |  Tiebreaker: Score → Rating → Visual Contrast → Review Count  |  Products shown: 15  |  Eliminated: 14</t>
+          <t>Generated: 2026-07-02  |  Products shown: 15  |  Eliminated by dedup rule: 14</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Weights applied:</t>
+          <t>Weights:</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Caregiver burden: 10%</t>
+          <t>caregiver burden: 10%</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Dementia suitability: 25%</t>
+          <t>dementia suitability: 25%</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Emotional comfort potential: 15%</t>
+          <t>emotional comfort potential: 15%</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>Noise sensitivity fit: 10%</t>
+          <t>sound quality: 10%</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>Recognizable pet appearance: 10%</t>
+          <t>recognizable pet appearance: 10%</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>Safety risk: 10%</t>
+          <t>safety risk: 10%</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>Simplicity of use: 20%</t>
+          <t>simplicity of use: 20%</t>
         </is>
       </c>
     </row>
@@ -690,8 +690,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Animal
-Type</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -732,7 +731,7 @@
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>noise sensitivity fit</t>
+          <t>sound quality</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
@@ -790,7 +789,7 @@
         <v>11640</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J5" s="8" t="n">
         <v>4</v>
@@ -802,7 +801,7 @@
         <v>5</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N5" s="8" t="n">
         <v>5</v>
@@ -815,7 +814,7 @@
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>All Joy for All variants share identical sensor/audio platform. Sound Quality=1 per locked rubric anchor (documented 'loud unrealistic meow', Best Buy reviews). Sound Level Control=5 per rubric anchor (3-position ON/OFF/MUTE switch). Review Strength=5 per verified 4.4/5 stars, 10,000+ Amazon reviews. Visual contrast varies by coat color — scored per variant. Orange tabby coat — higher visual contrast against most furniture. Review Strength=5: 11,640 reviews, 4.5★ (repo data, 2026-06-22).</t>
+          <t>All Joy for All variants share identical sensor/audio platform. Sound Quality=1 per locked rubric anchor (documented 'loud unrealistic meow', Best Buy reviews). Sound Level Control=5 per rubric anchor (3-position ON/OFF/MUTE switch). Review Strength=5 per verified 4.4/5 stars, 10,000+ Amazon reviews. Visual contrast varies by coat color — scored per variant. Orange tabby coat — higher visual contrast against most furniture. Review Strength=5: 11,640 reviews, 4.5★ (repo data, 2026-06-22). TACTILE COMFORT UPDATE (2026-07-01, Tim-directed): Rescored from 4 to 3. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier A — independent peer-reviewed research (Journal of Holistic Nursing, 2022). No cap; score reflects full 1-5 range. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=5, Safety=5, Calmness=avg(Sound=3, Behavioral Realism=3)=3.0. Raw average of 4 sub-criteria=4.5, rounded=5, Evidence Tier A cap=5 -&gt; Final=5 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -853,7 +852,7 @@
         <v>5164</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J6" s="12" t="n">
         <v>4</v>
@@ -865,7 +864,7 @@
         <v>5</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N6" s="12" t="n">
         <v>5</v>
@@ -878,7 +877,7 @@
       </c>
       <c r="Q6" s="11" t="inlineStr">
         <is>
-          <t>All Joy for All variants share identical sensor/audio platform. Sound Quality=1 per locked rubric anchor (documented 'loud unrealistic meow', Best Buy reviews). Sound Level Control=5 per rubric anchor (3-position ON/OFF/MUTE switch). Review Strength=5 per verified 4.4/5 stars, 10,000+ Amazon reviews. Visual contrast varies by coat color — scored per variant. Review Strength=5: 5,164 reviews, 4.3★ (repo data, 2026-06-22).</t>
+          <t>All Joy for All variants share identical sensor/audio platform. Sound Quality=1 per locked rubric anchor (documented 'loud unrealistic meow', Best Buy reviews). Sound Level Control=5 per rubric anchor (3-position ON/OFF/MUTE switch). Review Strength=5 per verified 4.4/5 stars, 10,000+ Amazon reviews. Visual contrast varies by coat color — scored per variant. Review Strength=5: 5,164 reviews, 4.3★ (repo data, 2026-06-22). TACTILE COMFORT UPDATE (2026-07-01, Tim-directed): Rescored from 4 to 3. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier A — independent peer-reviewed research (Journal of Holistic Nursing, 2022). No cap; score reflects full 1-5 range. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=5, Safety=5, Calmness=avg(Sound=3, Behavioral Realism=3)=3.0. Raw average of 4 sub-criteria=4.5, rounded=5, Evidence Tier A cap=5 -&gt; Final=5 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -916,7 +915,7 @@
         <v>16</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>4.25</v>
+        <v>4.35</v>
       </c>
       <c r="J7" s="8" t="n">
         <v>4</v>
@@ -928,7 +927,7 @@
         <v>5</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N7" s="8" t="n">
         <v>5</v>
@@ -941,7 +940,7 @@
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>Cat-form Percy model. Assumed feature parity with Percy 1.1 Robotic Dog. Review strength=3: lower cumulative reviews than Percy 1.1. Verify current features against chongker.com Percy Robot Cat listing before publishing. Review Strength=2: 16 reviews, 5★ (repo data, 2026-06-22).</t>
+          <t>Cat-form Percy model. Assumed feature parity with Percy 1.1 Robotic Dog. Review strength=3: lower cumulative reviews than Percy 1.1. Verify current features against chongker.com Percy Robot Cat listing before publishing. Review Strength=2: 16 reviews, 5★ (repo data, 2026-06-22). TACTILE COMFORT UPDATE (2026-07-01, Tim-directed): Rescored from 5 to 4. Percy line tier placed below MateCat (5) and above Joy for All (3) per Tim's tiering decision for the Chongker product family. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier C — dementia-suitability claims found only on Chongker's own marketing pages (unverified consultant/specialist quotes, no named institution); no independent research located. Capped at 4 per Tim's directive. Note: product complexity (voice commands, sleep-mode cycling, battery-status alerts on some models) also weighs against the Simplicity sub-criterion. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=4, Familiar Form=5, Safety=5, Calmness=avg(Sound=4, Behavioral Realism=4)=4.0. Raw average of 4 sub-criteria=4.5, rounded=5, Evidence Tier C cap=4 -&gt; Final=4 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -979,7 +978,7 @@
         <v>10</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>4.25</v>
+        <v>4.35</v>
       </c>
       <c r="J8" s="12" t="n">
         <v>4</v>
@@ -991,7 +990,7 @@
         <v>5</v>
       </c>
       <c r="M8" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N8" s="12" t="n">
         <v>5</v>
@@ -1004,7 +1003,7 @@
       </c>
       <c r="Q8" s="11" t="inlineStr">
         <is>
-          <t>Verified via Chongker instruction manual (manuals.plus/chongker/breathing-percy-cat-2-0-manual). Hybrid: combines breathing motion of Red Panda Plush WITH full Percy interactive features (touch sensors, heartbeat, voice wake, custom name, 4-level volume + silent). ON/PUR/OFF modes + volume +/- buttons. 180-day warranty per chongker.com. Privacy=5 confirmed: no camera or WiFi per Chongker product pattern. Review Strength=2: 10 reviews, 5★ (repo data, checked 2026-06-22).</t>
+          <t>Verified via Chongker instruction manual (manuals.plus/chongker/breathing-percy-cat-2-0-manual). Hybrid: combines breathing motion of Red Panda Plush WITH full Percy interactive features (touch sensors, heartbeat, voice wake, custom name, 4-level volume + silent). ON/PUR/OFF modes + volume +/- buttons. 180-day warranty per chongker.com. Privacy=5 confirmed: no camera or WiFi per Chongker product pattern. Review Strength=2: 10 reviews, 5★ (repo data, checked 2026-06-22). TACTILE COMFORT UPDATE (2026-07-01, Tim-directed): Rescored from 5 to 4. Percy line tier placed below MateCat (5) and above Joy for All (3) per Tim's tiering decision for the Chongker product family. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier C — dementia-suitability claims found only on Chongker's own marketing pages (unverified consultant/specialist quotes, no named institution); no independent research located. Capped at 4 per Tim's directive. Note: product complexity (voice commands, sleep-mode cycling, battery-status alerts on some models) also weighs against the Simplicity sub-criterion. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=4, Familiar Form=5, Safety=5, Calmness=avg(Sound=4, Behavioral Realism=3)=3.5. Raw average of 4 sub-criteria=4.38, rounded=4, Evidence Tier C cap=4 -&gt; Final=4 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1041,7 @@
         <v>5</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>4.25</v>
+        <v>4.35</v>
       </c>
       <c r="J9" s="8" t="n">
         <v>4</v>
@@ -1054,7 +1053,7 @@
         <v>5</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N9" s="8" t="n">
         <v>5</v>
@@ -1067,7 +1066,7 @@
       </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>Dog-form companion with touch sensors and heartbeat simulation. Weighted design for sensory relief per product documentation and buying-guide review (keyirobot.com). Feature set verified as broadly equivalent to MateCat Pro platform. Privacy=5: no camera or internet per Product Matrix. Product name updated to match repo: 'Percy 1.1 Robotic Companion Dog'. Review Strength=1: only 5 reviews at time of scoring (repo data, 2026-06-22).</t>
+          <t>Dog-form companion with touch sensors and heartbeat simulation. Weighted design for sensory relief per product documentation and buying-guide review (keyirobot.com). Feature set verified as broadly equivalent to MateCat Pro platform. Privacy=5: no camera or internet per Product Matrix. Product name updated to match repo: 'Percy 1.1 Robotic Companion Dog'. Review Strength=1: only 5 reviews at time of scoring (repo data, 2026-06-22). TACTILE COMFORT UPDATE (2026-07-01, Tim-directed): Rescored from 5 to 4. Percy line tier placed below MateCat (5) and above Joy for All (3) per Tim's tiering decision for the Chongker product family. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier C — dementia-suitability claims found only on Chongker's own marketing pages (unverified consultant/specialist quotes, no named institution); no independent research located. Capped at 4 per Tim's directive. Note: product complexity (voice commands, sleep-mode cycling, battery-status alerts on some models) also weighs against the Simplicity sub-criterion. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=4, Familiar Form=5, Safety=5, Calmness=avg(Sound=4, Behavioral Realism=4)=4.0. Raw average of 4 sub-criteria=4.5, rounded=5, Evidence Tier C cap=4 -&gt; Final=4 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1104,8 +1103,8 @@
       <c r="H10" s="12" t="n">
         <v>1200</v>
       </c>
-      <c r="I10" s="13" t="n">
-        <v>4.1</v>
+      <c r="I10" s="14" t="n">
+        <v>3.8</v>
       </c>
       <c r="J10" s="12" t="n">
         <v>5</v>
@@ -1117,7 +1116,7 @@
         <v>3</v>
       </c>
       <c r="M10" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N10" s="12" t="n">
         <v>4</v>
@@ -1130,7 +1129,7 @@
       </c>
       <c r="Q10" s="11" t="inlineStr">
         <is>
-          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Quality=1 and Sound Level Control=1 — product produces no sounds; scores reflect absence of any sound output (lowest possible score on both scales). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Black/white coat: high contrast, distinctive visibility. Product name updated: 'Original Black and White Shorthair Cat' per repo. Review Strength=4: 1200 reviews, 4.4★ (repo, 2026-06-22). SOUND QUALITY FLAG: With budget barking dogs=1 and Joy for All=3, Perfect Petzzz (no sounds at all) may need reconsideration — currently 1 pending Tim review.</t>
+          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Black/white coat: high contrast, distinctive visibility. Product name updated: 'Original Black and White Shorthair Cat' per repo. Review Strength=4: 1200 reviews, 4.4★ (repo, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1167,8 +1166,8 @@
       <c r="H11" s="8" t="n">
         <v>466</v>
       </c>
-      <c r="I11" s="9" t="n">
-        <v>4.1</v>
+      <c r="I11" s="15" t="n">
+        <v>3.8</v>
       </c>
       <c r="J11" s="8" t="n">
         <v>5</v>
@@ -1180,7 +1179,7 @@
         <v>3</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N11" s="8" t="n">
         <v>4</v>
@@ -1193,7 +1192,7 @@
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Quality=1 and Sound Level Control=1 — product produces no sounds; scores reflect absence of any sound output (lowest possible score on both scales). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Product name updated: 'Original Beagle' per repo. Review Strength=3: 466 reviews, 4.4★ (repo, 2026-06-22). SOUND QUALITY FLAG: With budget barking dogs=1 and Joy for All=3, Perfect Petzzz (no sounds at all) may need reconsideration — currently 1 pending Tim review.</t>
+          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Product name updated: 'Original Beagle' per repo. Review Strength=3: 466 reviews, 4.4★ (repo, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1230,7 @@
         <v>2</v>
       </c>
       <c r="I12" s="14" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="J12" s="12" t="n">
         <v>4</v>
@@ -1243,7 +1242,7 @@
         <v>4</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>3</v>
@@ -1256,7 +1255,7 @@
       </c>
       <c r="Q12" s="11" t="inlineStr">
         <is>
-          <t>Detailed scoring performed in prior session against original product spec sheet. Review Strength: no verified current Amazon rating found — manual lookup required before publishing. Control accessibility=3: single ear-switch concealed in fur. Noise Sensitivity=5: explicit mute mode, designed to avoid motor noise per manufacturer. Amazon listing confirmed by Tim: https://www.amazon.com/Chongker-Breathing-Soothing-Interactive-Companion/dp/B0F83R6F75 — Amazon automated access blocked; star rating and review count require manual lookup before updating Review Strength score. Review Strength=1: only 2 reviews at time of scoring (repo data, 2026-06-22). Amazon URL confirmed: amazon.com/dp/B0F83R6F75 — automated fetch blocked; verify rating/count manually before next refresh Value for Money forced to 4 by Tim (June 2026) — consistent with other Chongker product family scores. See Product_Feature_Score_Details.xlsx for rationale.</t>
+          <t>Detailed scoring performed in prior session against original product spec sheet. Review Strength: no verified current Amazon rating found — manual lookup required before publishing. Control accessibility=3: single ear-switch concealed in fur. Noise Sensitivity=5: explicit mute mode, designed to avoid motor noise per manufacturer. Amazon listing confirmed by Tim: https://www.amazon.com/Chongker-Breathing-Soothing-Interactive-Companion/dp/B0F83R6F75 — Amazon automated access blocked; star rating and review count require manual lookup before updating Review Strength score. Review Strength=1: only 2 reviews at time of scoring (repo data, 2026-06-22). Amazon URL confirmed: amazon.com/dp/B0F83R6F75 — automated fetch blocked; verify rating/count manually before next refresh Value for Money forced to 4 by Tim (June 2026) — consistent with other Chongker product family scores. See Product_Feature_Score_Details.xlsx for rationale. TACTILE COMFORT REVIEW (2026-07-01): Considered for reclassification from MateCat tier (5) to Percy tier (4) alongside other Chongker Tactile Comfort changes. Manufacturer/Amazon listing describes cloud-like softness, silicone 'toe beans', and seamless ultra-soft faux fur construction with no competing hard internal mechanisms (no sensors/movement hardware, unlike Percy/MateCat robotic lines) — tactile comfort is the product's primary marketed feature. No independent (non-manufacturer) reviews found directly comparing its fur/feel against MateCat or Percy. Tim confirmed keeping this at 5 (MateCat tier) based on this evidence. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier C — dementia-suitability claims found only on Chongker's own marketing pages (unverified consultant/specialist quotes, no named institution); no independent research located. Capped at 4 per Tim's directive. Note: product complexity (voice commands, sleep-mode cycling, battery-status alerts on some models) also weighs against the Simplicity sub-criterion. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=4, Familiar Form=3, Safety=4, Calmness=avg(Sound=4, Behavioral Realism=1)=2.5. Raw average of 4 sub-criteria=3.38, rounded=3, Evidence Tier C cap=4 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1266,17 +1265,17 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Ropet</t>
+          <t>Furby</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>KAMOMO</t>
+          <t>DJ Furby</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>Budget Friendly</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -1285,16 +1284,16 @@
         </is>
       </c>
       <c r="F13" s="8" t="n">
-        <v>349</v>
+        <v>50.11</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>17</v>
+        <v>772</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="J13" s="8" t="n">
         <v>4</v>
@@ -1303,23 +1302,23 @@
         <v>3</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M13" s="8" t="n">
         <v>3</v>
       </c>
       <c r="N13" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O13" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P13" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>Founded 2022; CES 2025 debut; Series A1 funded (Beijing AI Industry Investment Fund). Privacy=3: local offline AI for daily use; photo uploads encrypted on-device before cloud (ropetai.com). 39°C bionic warmth feature unique in this market (verified Amazon B0GTPZ4N4M). Stationary desktop companion — no locomotion (Movement=1). Brand Reliability=3: legitimate but newer; 30-day returns per manufacturer. Review strength=3: growing — recommend re-check as product matures. Review Strength=2: 17 reviews, 4.3★ (repo data, 2026-06-22).</t>
+          <t>Hasbro 2023 'Hey Furby' — 25th anniversary edition. No app, no WiFi, no Bluetooth confirmed (Official Furby Wiki; IEEE Spectrum). 4x AA batteries. 5 voice-activated modes, 600+ pre-programmed reactions. Sound Level Control=2: no volume adjustment available (documented consumer complaint); only shutdown or mode switching. Brand=5: Hasbro, globally established, 58M+ units sold over 25 years. Review Strength=5: massive lifetime Amazon review volume. Dementia=2: loud/unpredictable, fantastical non-animal appearance — not recommended for memory care. Privacy=5: confirmed no wireless connectivity in 2023 model. IMPORTANT: DJ Furby (2025) is a different model from the Furby 2023 originally scored — elongated 'long oddbody' form factor with DJ/music theme (per Official Furby Wiki). Core feature scores carried over from 2023 Furby as closest available data; verify DJ-specific features (music modes, controls, form factor) before publishing. Review Strength=4: 772 reviews, 4.8★ (repo data, 2026-06-22). Visual contrast likely higher than regular Furby due to distinctive elongated DJ styling. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=4, Familiar Form=3, Safety=5, Calmness=avg(Sound=3, Behavioral Realism=3)=3.0. Raw average of 4 sub-criteria=3.75, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (was 2). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1329,17 +1328,17 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Furby</t>
+          <t>Ropet</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>DJ Furby</t>
+          <t>KAMOMO</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Budget Friendly</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
@@ -1348,41 +1347,41 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>50.11</v>
+        <v>349</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>772</v>
+        <v>17</v>
       </c>
       <c r="I14" s="14" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="J14" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K14" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M14" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="N14" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L14" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="M14" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="N14" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="O14" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P14" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q14" s="11" t="inlineStr">
         <is>
-          <t>Hasbro 2023 'Hey Furby' — 25th anniversary edition. No app, no WiFi, no Bluetooth confirmed (Official Furby Wiki; IEEE Spectrum). 4x AA batteries. 5 voice-activated modes, 600+ pre-programmed reactions. Sound Level Control=2: no volume adjustment available (documented consumer complaint); only shutdown or mode switching. Brand=5: Hasbro, globally established, 58M+ units sold over 25 years. Review Strength=5: massive lifetime Amazon review volume. Dementia=2: loud/unpredictable, fantastical non-animal appearance — not recommended for memory care. Privacy=5: confirmed no wireless connectivity in 2023 model. IMPORTANT: DJ Furby (2025) is a different model from the Furby 2023 originally scored — elongated 'long oddbody' form factor with DJ/music theme (per Official Furby Wiki). Core feature scores carried over from 2023 Furby as closest available data; verify DJ-specific features (music modes, controls, form factor) before publishing. Review Strength=4: 772 reviews, 4.8★ (repo data, 2026-06-22). Visual contrast likely higher than regular Furby due to distinctive elongated DJ styling.</t>
+          <t>Founded 2022; CES 2025 debut; Series A1 funded (Beijing AI Industry Investment Fund). Privacy=3: local offline AI for daily use; photo uploads encrypted on-device before cloud (ropetai.com). 39°C bionic warmth feature unique in this market (verified Amazon B0GTPZ4N4M). Stationary desktop companion — no locomotion (Movement=1). Brand Reliability=3: legitimate but newer; 30-day returns per manufacturer. Review strength=3: growing — recommend re-check as product matures. Review Strength=2: 17 reviews, 4.3★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=3, Familiar Form=2, Safety=4, Calmness=avg(Sound=3, Behavioral Realism=2)=2.5. Raw average of 4 sub-criteria=2.88, rounded=3, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1419,14 +1418,14 @@
       <c r="H15" s="8" t="n">
         <v>80</v>
       </c>
-      <c r="I15" s="16" t="n">
-        <v>2.85</v>
+      <c r="I15" s="15" t="n">
+        <v>3.1</v>
       </c>
       <c r="J15" s="8" t="n">
         <v>4</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L15" s="8" t="n">
         <v>3</v>
@@ -1445,7 +1444,7 @@
       </c>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>WARNING — LOW CONFIDENCE ACROSS ALL SCORES. No verified independent reviews found; all scores based on wuffyrobot.com marketing claims only. Review Strength=1: no verifiable third-party reviews identified. Brand Reliability=2: new/unverifiable brand, no established track record. Return/Gift Suitability=2: return policy unclear from DTC site. Recommend independent verification of product claims before featuring on site. Compare against Puppy Milow profile for scam-risk indicators. Review Strength=2: 80 reviews but only 3★ (repo data, 2026-06-22). Low rating confirms earlier caution flag about product quality/marketing claims.</t>
+          <t>WARNING — LOW CONFIDENCE ACROSS ALL SCORES. No verified independent reviews found; all scores based on wuffyrobot.com marketing claims only. Review Strength=1: no verifiable third-party reviews identified. Brand Reliability=2: new/unverifiable brand, no established track record. Return/Gift Suitability=2: return policy unclear from DTC site. Recommend independent verification of product claims before featuring on site. Compare against Puppy Milow profile for scam-risk indicators. Review Strength=2: 80 reviews but only 3★ (repo data, 2026-06-22). Low rating confirms earlier caution flag about product quality/marketing claims. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=3, Familiar Form=3, Safety=4, Calmness=avg(Sound=2, Behavioral Realism=2)=2.0. Raw average of 4 sub-criteria=3.0, rounded=3, Evidence Tier D cap=3 -&gt; Final=3 (was 2). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1482,14 +1481,14 @@
       <c r="H16" s="12" t="n">
         <v>283</v>
       </c>
-      <c r="I16" s="17" t="n">
-        <v>2.35</v>
+      <c r="I16" s="16" t="n">
+        <v>2.85</v>
       </c>
       <c r="J16" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L16" s="12" t="n">
         <v>2</v>
@@ -1508,7 +1507,7 @@
       </c>
       <c r="Q16" s="11" t="inlineStr">
         <is>
-          <t>Children's programmable toy robot dog with remote/gesture control. No WiFi or app required (infrared remote — Privacy=5). Hard plastic ABS shell, LED facial expressions, walks/spins/dances. 30-day returns, 90-day warranty per Amazon listing (B0FLXCXPHD). Sound Level Control=2: no volume adjustment noted; on/off states only. Dementia=1: remote-controlled, LED face, not a calming companion product. Not recommended for senior care use cases. Review Strength=3: 283 reviews, 4.4★ (repo data, 2026-06-22).</t>
+          <t>Children's programmable toy robot dog with remote/gesture control. No WiFi or app required (infrared remote — Privacy=5). Hard plastic ABS shell, LED facial expressions, walks/spins/dances. 30-day returns, 90-day warranty per Amazon listing (B0FLXCXPHD). Sound Level Control=2: no volume adjustment noted; on/off states only. Dementia=1: remote-controlled, LED face, not a calming companion product. Not recommended for senior care use cases. Review Strength=3: 283 reviews, 4.4★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=3, Familiar Form=3, Safety=3, Calmness=avg(Sound=2, Behavioral Realism=2)=2.0. Raw average of 4 sub-criteria=2.75, rounded=3, Evidence Tier D cap=3 -&gt; Final=3 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1518,60 +1517,60 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Enabot</t>
+          <t>Loona</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>ROLA Mini Pet Monitor</t>
+          <t>Robot Pet Dog</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Best Value</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Robot</t>
+          <t>Dog</t>
         </is>
       </c>
       <c r="F17" s="8" t="n">
-        <v>139</v>
+        <v>499</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>73</v>
-      </c>
-      <c r="I17" s="16" t="n">
-        <v>1.6</v>
+        <v>1199</v>
+      </c>
+      <c r="I17" s="17" t="n">
+        <v>1.95</v>
       </c>
       <c r="J17" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K17" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N17" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O17" s="8" t="n">
         <v>2</v>
       </c>
       <c r="P17" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>Camera=yes, Internet Access=yes per Product Matrix. Hard-shell rolling security camera robot; not a companion pet. Scores are category-level; minor spec differences between models noted. Review strength and Value estimated — recommend manual Amazon verification. ROLA Mini is the most compact Enabot; Size=5. Charging=4 (dock, but smaller form factor). Product renamed to 'ROLA Mini Pet Monitor'. Review Strength=3: 73 reviews, 5★ (repo data, 2026-06-22).</t>
+          <t>KEYi Tech Loona. Rubric anchor product: Control Accessibility=1 (worst) and Customization Options=5 (best). ChatGPT-4o integration. Camera, WiFi, app, account all required. Camera=yes, Internet Access=yes per Product Matrix. Voice=4: excellent AI voice response but conversational not animal-mimicry. Not recommended for seniors or dementia care. Review Strength=4: 1,199 reviews, 4.2★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=1, Familiar Form=2, Safety=2, Calmness=avg(Sound=3, Behavioral Realism=2)=2.5. Raw average of 4 sub-criteria=1.88, rounded=2, Evidence Tier D cap=3 -&gt; Final=2 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1586,12 +1585,12 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>EBO Air 2 Plus FamilyBot</t>
+          <t>ROLA Mini Pet Monitor</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>Best Value</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
@@ -1600,28 +1599,28 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>359</v>
+        <v>139</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="I18" s="17" t="n">
-        <v>1.6</v>
+        <v>73</v>
+      </c>
+      <c r="I18" s="16" t="n">
+        <v>1.75</v>
       </c>
       <c r="J18" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>1</v>
@@ -1634,7 +1633,7 @@
       </c>
       <c r="Q18" s="11" t="inlineStr">
         <is>
-          <t>Camera=yes, Internet Access=yes per Product Matrix. Hard-shell rolling security camera robot; not a companion pet. Scores are category-level; minor spec differences between models noted. Review strength and Value estimated — recommend manual Amazon verification. Air 2 Plus has AI chat mode — highest AI tier in Enabot lineup per manufacturer. Product renamed to 'EBO Air 2 Plus FamilyBot'. Review Strength=3: 42 reviews, 5★ (repo data, 2026-06-22).</t>
+          <t>Camera=yes, Internet Access=yes per Product Matrix. Hard-shell rolling security camera robot; not a companion pet. Scores are category-level; minor spec differences between models noted. Review strength and Value estimated — recommend manual Amazon verification. ROLA Mini is the most compact Enabot; Size=5. Charging=4 (dock, but smaller form factor). Product renamed to 'ROLA Mini Pet Monitor'. Review Strength=3: 73 reviews, 5★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=2, Familiar Form=1, Safety=2, Calmness=avg(Sound=3, Behavioral Realism=1)=2.0. Raw average of 4 sub-criteria=1.75, rounded=2, Evidence Tier D cap=3 -&gt; Final=2 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1643,12 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Loona</t>
+          <t>Enabot</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Robot Pet Dog</t>
+          <t>EBO Air 2 Plus FamilyBot</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -1659,53 +1658,53 @@
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Robot</t>
         </is>
       </c>
       <c r="F19" s="8" t="n">
-        <v>499</v>
+        <v>359</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>1199</v>
-      </c>
-      <c r="I19" s="16" t="n">
-        <v>1.6</v>
+        <v>42</v>
+      </c>
+      <c r="I19" s="17" t="n">
+        <v>1.75</v>
       </c>
       <c r="J19" s="8" t="n">
         <v>1</v>
       </c>
       <c r="K19" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="L19" s="8" t="n">
-        <v>3</v>
-      </c>
       <c r="M19" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N19" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O19" s="8" t="n">
         <v>2</v>
       </c>
       <c r="P19" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="7" t="inlineStr">
         <is>
-          <t>KEYi Tech Loona. Rubric anchor product: Control Accessibility=1 (worst) and Customization Options=5 (best). ChatGPT-4o integration. Camera, WiFi, app, account all required. Camera=yes, Internet Access=yes per Product Matrix. Voice=4: excellent AI voice response but conversational not animal-mimicry. Not recommended for seniors or dementia care. Review Strength=4: 1,199 reviews, 4.2★ (repo data, 2026-06-22).</t>
+          <t>Camera=yes, Internet Access=yes per Product Matrix. Hard-shell rolling security camera robot; not a companion pet. Scores are category-level; minor spec differences between models noted. Review strength and Value estimated — recommend manual Amazon verification. Air 2 Plus has AI chat mode — highest AI tier in Enabot lineup per manufacturer. Product renamed to 'EBO Air 2 Plus FamilyBot'. Review Strength=3: 42 reviews, 5★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=2, Familiar Form=1, Safety=2, Calmness=avg(Sound=3, Behavioral Realism=1)=2.0. Raw average of 4 sub-criteria=1.75, rounded=2, Evidence Tier D cap=3 -&gt; Final=2 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:O1"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1733,7 +1732,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>Eliminated products — Best for Seniors with Dementia  (same Manufacturer × Price Category × Animal Category slot as a higher-scoring product)</t>
+          <t>Eliminated by dedup rule — Best for Seniors with Dementia  (same Manufacturer x Price Category x Animal Category as a higher-scoring product)</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1754,7 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Animal</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -1801,7 +1800,7 @@
         </is>
       </c>
       <c r="E3" s="19" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="F3" s="19" t="n">
         <v>4.5</v>
@@ -1813,7 +1812,7 @@
       </c>
       <c r="H3" s="19" t="inlineStr">
         <is>
-          <t>Score=4.50 rating=4.5</t>
+          <t>score=4.70 rating=4.5</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1838,7 @@
         </is>
       </c>
       <c r="E4" s="20" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="F4" s="20" t="n">
         <v>4.5</v>
@@ -1851,7 +1850,7 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>Score=4.50 rating=4.5</t>
+          <t>score=4.70 rating=4.5</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1876,7 @@
         </is>
       </c>
       <c r="E5" s="19" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="F5" s="19" t="n">
         <v>4.3</v>
@@ -1889,7 +1888,7 @@
       </c>
       <c r="H5" s="19" t="inlineStr">
         <is>
-          <t>Score=4.50 rating=4.3</t>
+          <t>score=4.70 rating=4.3</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1914,7 @@
         </is>
       </c>
       <c r="E6" s="20" t="n">
-        <v>4.25</v>
+        <v>4.35</v>
       </c>
       <c r="F6" s="20" t="n">
         <v>4.6</v>
@@ -1927,24 +1926,24 @@
       </c>
       <c r="H6" s="20" t="inlineStr">
         <is>
-          <t>Score=4.25 rating=4.6</t>
+          <t>score=4.35 rating=4.6</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>Perfect Petzzz</t>
+          <t>Chongker</t>
         </is>
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>Grey Tabby Cat</t>
+          <t>MateCat 1.1</t>
         </is>
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t>Budget Friendly</t>
+          <t>Best Value</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
@@ -1953,19 +1952,19 @@
         </is>
       </c>
       <c r="E7" s="19" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="G7" s="19" t="inlineStr">
         <is>
-          <t>Original Black and White Shorthair Cat</t>
+          <t>Breathing Calico Percy 2.0</t>
         </is>
       </c>
       <c r="H7" s="19" t="inlineStr">
         <is>
-          <t>Score=4.10 rating=4.3</t>
+          <t>score=4.20 rating=4</t>
         </is>
       </c>
     </row>
@@ -1977,7 +1976,7 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Original Siamese Cat</t>
+          <t>Grey Tabby Cat</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -1991,10 +1990,10 @@
         </is>
       </c>
       <c r="E8" s="20" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="F8" s="20" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="G8" s="20" t="inlineStr">
         <is>
@@ -2003,7 +2002,7 @@
       </c>
       <c r="H8" s="20" t="inlineStr">
         <is>
-          <t>Score=4.10 rating=4.1</t>
+          <t>score=3.80 rating=4.3</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2014,7 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>Original Plush White Cat</t>
+          <t>Original Siamese Cat</t>
         </is>
       </c>
       <c r="C9" s="19" t="inlineStr">
@@ -2029,11 +2028,11 @@
         </is>
       </c>
       <c r="E9" s="19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F9" s="19" t="n">
         <v>4.1</v>
       </c>
-      <c r="F9" s="19" t="n">
-        <v>4</v>
-      </c>
       <c r="G9" s="19" t="inlineStr">
         <is>
           <t>Original Black and White Shorthair Cat</t>
@@ -2041,7 +2040,7 @@
       </c>
       <c r="H9" s="19" t="inlineStr">
         <is>
-          <t>Score=4.10 rating=4</t>
+          <t>score=3.80 rating=4.1</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2052,7 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Original Chocolate Lab</t>
+          <t>Original Plush White Cat</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -2063,23 +2062,23 @@
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Cat</t>
         </is>
       </c>
       <c r="E10" s="20" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="F10" s="20" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="G10" s="20" t="inlineStr">
         <is>
-          <t>Original Beagle</t>
+          <t>Original Black and White Shorthair Cat</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
         <is>
-          <t>Score=4.10 rating=4.3</t>
+          <t>score=3.80 rating=4</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2090,7 @@
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>Original Border Collie</t>
+          <t>Original Chocolate Lab</t>
         </is>
       </c>
       <c r="C11" s="19" t="inlineStr">
@@ -2105,7 +2104,7 @@
         </is>
       </c>
       <c r="E11" s="19" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="F11" s="19" t="n">
         <v>4.3</v>
@@ -2117,7 +2116,7 @@
       </c>
       <c r="H11" s="19" t="inlineStr">
         <is>
-          <t>Score=4.10 rating=4.3</t>
+          <t>score=3.80 rating=4.3</t>
         </is>
       </c>
     </row>
@@ -2129,7 +2128,7 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Original Shih Tzu</t>
+          <t>Original Border Collie</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -2143,10 +2142,10 @@
         </is>
       </c>
       <c r="E12" s="20" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="F12" s="20" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G12" s="20" t="inlineStr">
         <is>
@@ -2155,45 +2154,45 @@
       </c>
       <c r="H12" s="20" t="inlineStr">
         <is>
-          <t>Score=4.10 rating=4.2</t>
+          <t>score=3.80 rating=4.3</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
         <is>
-          <t>Chongker</t>
+          <t>Perfect Petzzz</t>
         </is>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>MateCat 1.1</t>
+          <t>Original Shih Tzu</t>
         </is>
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
-          <t>Best Value</t>
+          <t>Budget Friendly</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
-          <t>Cat</t>
+          <t>Dog</t>
         </is>
       </c>
       <c r="E13" s="19" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="G13" s="19" t="inlineStr">
         <is>
-          <t>Breathing Calico Percy 2.0</t>
+          <t>Original Beagle</t>
         </is>
       </c>
       <c r="H13" s="19" t="inlineStr">
         <is>
-          <t>Score=3.85 rating=4</t>
+          <t>score=3.80 rating=4.2</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2218,7 @@
         </is>
       </c>
       <c r="E14" s="20" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="F14" s="20" t="n">
         <v>4.5</v>
@@ -2231,7 +2230,7 @@
       </c>
       <c r="H14" s="20" t="inlineStr">
         <is>
-          <t>Score=1.60 rating=4.5</t>
+          <t>score=1.75 rating=4.5</t>
         </is>
       </c>
     </row>
@@ -2257,7 +2256,7 @@
         </is>
       </c>
       <c r="E15" s="19" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="F15" s="19" t="n">
         <v>5</v>
@@ -2269,7 +2268,7 @@
       </c>
       <c r="H15" s="19" t="inlineStr">
         <is>
-          <t>Score=1.60 rating=5</t>
+          <t>score=1.75 rating=5</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2294,7 @@
         </is>
       </c>
       <c r="E16" s="20" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="F16" s="20" t="n">
         <v>4.5</v>
@@ -2307,7 +2306,7 @@
       </c>
       <c r="H16" s="20" t="inlineStr">
         <is>
-          <t>Score=1.60 rating=4.5</t>
+          <t>score=1.75 rating=4.5</t>
         </is>
       </c>
     </row>
@@ -2400,12 +2399,12 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>Overall fit for memory care: simplicity, familiar form, calmness, safety</t>
+          <t>Overall fit for memory care, assessed via four sub-criteria: Simplicity (no memorized commands/phrases, minimal buttons or menus, no charging-status literacy required), Familiar Form (reuses 'Recognizable pet appearance' score), Calmness (predictable, non-jarring interaction; informed by 'Sound quality' and realism), and Safety (reuses 'Safety risk' score). Each score must be tagged in Notes with an Evidence Tier (see Score Type) reflecting the strength of dementia-specific support behind it.</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t>1 – 5</t>
+          <t>1-5. EVIDENCE TIERS (determine max score): Tier A = independent peer-reviewed research specific to the product (no cap, full 1-5 range). Tier B = independent caregiver/facility evidence — verified reviews, news coverage, facility pilot reports; NOT manufacturer-published (capped at 4). Tier C = manufacturer marketing claims only, no independent verification (capped at 4, per Tim 7/2026 — raised from initial proposal of 3). Tier D = no dementia-specific evidence found; scored by sub-criteria judgment alone (capped at 3).</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2433,7 @@
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
-          <t>noise sensitivity fit</t>
+          <t>sound quality</t>
         </is>
       </c>
       <c r="B6" s="24" t="inlineStr">
@@ -2444,14 +2443,12 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>Suitable for people startled by sudden sound or quiet environments</t>
+          <t>Whether sounds are soothing, realistic, or unsettling — including verified reports in retailer reviews (Amazon, Best Buy, Walmart) of a product startling users or being unsuitable for noise-sensitive/quiet environments. As of 2026-07, this feature absorbs the former 'Noise sensitivity fit' feature (eliminated as a separate row — overlapping scope). Products that produce no sound of any kind are scored N/A, not on the 1-5 scale.</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>1 – 5
-(reversed:
-5 = quiet)</t>
+          <t>1 - 5, or N/A if the product produces no sound of any kind</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2520,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="16" customHeight="1">
+    <row r="10">
       <c r="A10" s="25" t="inlineStr">
         <is>
           <t>TOTAL</t>

--- a/Documentation/Best For Lists/Best for Seniors with Dementia List.xlsx
+++ b/Documentation/Best For Lists/Best for Seniors with Dementia List.xlsx
@@ -195,10 +195,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -588,7 +588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -620,7 +620,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-02  |  Products shown: 15  |  Eliminated by dedup rule: 14</t>
+          <t>Generated: 2026-07-07  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Original Black and White Shorthair Cat</t>
+          <t>Grey Tabby Cat</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -1098,10 +1098,10 @@
         <v>44.45</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>1200</v>
+        <v>848</v>
       </c>
       <c r="I10" s="14" t="n">
         <v>3.8</v>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="Q10" s="11" t="inlineStr">
         <is>
-          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Black/white coat: high contrast, distinctive visibility. Product name updated: 'Original Black and White Shorthair Cat' per repo. Review Strength=4: 1200 reviews, 4.4★ (repo, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Previously scored as 'Calico Cat' — now matched to 'Grey Tabby Cat' per repo. Verify this is the correct product match before publishing. Review Strength=4: 848 reviews, 4.3★ (repo data, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Original Beagle</t>
+          <t>Original Chocolate Lab</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -1161,10 +1161,10 @@
         <v>44.45</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>466</v>
+        <v>553</v>
       </c>
       <c r="I11" s="15" t="n">
         <v>3.8</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Product name updated: 'Original Beagle' per repo. Review Strength=3: 466 reviews, 4.4★ (repo, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Product name updated: 'Original Chocolate Lab' per repo. Review Strength=4: 553 reviews, 4.3★ (repo, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1202,60 +1202,58 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Chongker</t>
+          <t>Perfect Petzzz</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Breathing Red Panda Plush</t>
+          <t>Original Black and White Shorthair Cat</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Best Value</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>Panda</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="n">
-        <v>119</v>
-      </c>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J12" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M12" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I12" s="14" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="J12" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K12" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="M12" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="N12" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P12" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q12" s="11" t="inlineStr">
         <is>
-          <t>Detailed scoring performed in prior session against original product spec sheet. Review Strength: no verified current Amazon rating found — manual lookup required before publishing. Control accessibility=3: single ear-switch concealed in fur. Noise Sensitivity=5: explicit mute mode, designed to avoid motor noise per manufacturer. Amazon listing confirmed by Tim: https://www.amazon.com/Chongker-Breathing-Soothing-Interactive-Companion/dp/B0F83R6F75 — Amazon automated access blocked; star rating and review count require manual lookup before updating Review Strength score. Review Strength=1: only 2 reviews at time of scoring (repo data, 2026-06-22). Amazon URL confirmed: amazon.com/dp/B0F83R6F75 — automated fetch blocked; verify rating/count manually before next refresh Value for Money forced to 4 by Tim (June 2026) — consistent with other Chongker product family scores. See Product_Feature_Score_Details.xlsx for rationale. TACTILE COMFORT REVIEW (2026-07-01): Considered for reclassification from MateCat tier (5) to Percy tier (4) alongside other Chongker Tactile Comfort changes. Manufacturer/Amazon listing describes cloud-like softness, silicone 'toe beans', and seamless ultra-soft faux fur construction with no competing hard internal mechanisms (no sensors/movement hardware, unlike Percy/MateCat robotic lines) — tactile comfort is the product's primary marketed feature. No independent (non-manufacturer) reviews found directly comparing its fur/feel against MateCat or Percy. Tim confirmed keeping this at 5 (MateCat tier) based on this evidence. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier C — dementia-suitability claims found only on Chongker's own marketing pages (unverified consultant/specialist quotes, no named institution); no independent research located. Capped at 4 per Tim's directive. Note: product complexity (voice commands, sleep-mode cycling, battery-status alerts on some models) also weighs against the Simplicity sub-criterion. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=4, Familiar Form=3, Safety=4, Calmness=avg(Sound=4, Behavioral Realism=1)=2.5. Raw average of 4 sub-criteria=3.38, rounded=3, Evidence Tier C cap=4 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Black/white coat: high contrast, distinctive visibility. Product name updated: 'Original Black and White Shorthair Cat' per repo. Review Strength=4: 1200 reviews, 4.4★ (repo, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1265,35 +1263,35 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Furby</t>
+          <t>Chongker</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>DJ Furby</t>
+          <t>Breathing Red Panda Plush</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Budget Friendly</t>
+          <t>Best Value</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Robot</t>
+          <t>Panda</t>
         </is>
       </c>
       <c r="F13" s="8" t="n">
-        <v>50.11</v>
+        <v>119</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>772</v>
+        <v>2</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="J13" s="8" t="n">
         <v>4</v>
@@ -1302,23 +1300,23 @@
         <v>3</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N13" s="8" t="n">
         <v>3</v>
       </c>
       <c r="O13" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P13" s="8" t="n">
         <v>4</v>
       </c>
       <c r="Q13" s="7" t="inlineStr">
         <is>
-          <t>Hasbro 2023 'Hey Furby' — 25th anniversary edition. No app, no WiFi, no Bluetooth confirmed (Official Furby Wiki; IEEE Spectrum). 4x AA batteries. 5 voice-activated modes, 600+ pre-programmed reactions. Sound Level Control=2: no volume adjustment available (documented consumer complaint); only shutdown or mode switching. Brand=5: Hasbro, globally established, 58M+ units sold over 25 years. Review Strength=5: massive lifetime Amazon review volume. Dementia=2: loud/unpredictable, fantastical non-animal appearance — not recommended for memory care. Privacy=5: confirmed no wireless connectivity in 2023 model. IMPORTANT: DJ Furby (2025) is a different model from the Furby 2023 originally scored — elongated 'long oddbody' form factor with DJ/music theme (per Official Furby Wiki). Core feature scores carried over from 2023 Furby as closest available data; verify DJ-specific features (music modes, controls, form factor) before publishing. Review Strength=4: 772 reviews, 4.8★ (repo data, 2026-06-22). Visual contrast likely higher than regular Furby due to distinctive elongated DJ styling. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=4, Familiar Form=3, Safety=5, Calmness=avg(Sound=3, Behavioral Realism=3)=3.0. Raw average of 4 sub-criteria=3.75, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (was 2). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>Detailed scoring performed in prior session against original product spec sheet. Review Strength: no verified current Amazon rating found — manual lookup required before publishing. Control accessibility=3: single ear-switch concealed in fur. Noise Sensitivity=5: explicit mute mode, designed to avoid motor noise per manufacturer. Amazon listing confirmed by Tim: https://www.amazon.com/Chongker-Breathing-Soothing-Interactive-Companion/dp/B0F83R6F75 — Amazon automated access blocked; star rating and review count require manual lookup before updating Review Strength score. Review Strength=1: only 2 reviews at time of scoring (repo data, 2026-06-22). Amazon URL confirmed: amazon.com/dp/B0F83R6F75 — automated fetch blocked; verify rating/count manually before next refresh Value for Money forced to 4 by Tim (June 2026) — consistent with other Chongker product family scores. See Product_Feature_Score_Details.xlsx for rationale. TACTILE COMFORT REVIEW (2026-07-01): Considered for reclassification from MateCat tier (5) to Percy tier (4) alongside other Chongker Tactile Comfort changes. Manufacturer/Amazon listing describes cloud-like softness, silicone 'toe beans', and seamless ultra-soft faux fur construction with no competing hard internal mechanisms (no sensors/movement hardware, unlike Percy/MateCat robotic lines) — tactile comfort is the product's primary marketed feature. No independent (non-manufacturer) reviews found directly comparing its fur/feel against MateCat or Percy. Tim confirmed keeping this at 5 (MateCat tier) based on this evidence. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier C — dementia-suitability claims found only on Chongker's own marketing pages (unverified consultant/specialist quotes, no named institution); no independent research located. Capped at 4 per Tim's directive. Note: product complexity (voice commands, sleep-mode cycling, battery-status alerts on some models) also weighs against the Simplicity sub-criterion. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=4, Familiar Form=3, Safety=4, Calmness=avg(Sound=4, Behavioral Realism=1)=2.5. Raw average of 4 sub-criteria=3.38, rounded=3, Evidence Tier C cap=4 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1328,17 +1326,17 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Ropet</t>
+          <t>Furby</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>KAMOMO</t>
+          <t>DJ Furby</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>Budget Friendly</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
@@ -1347,16 +1345,16 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>349</v>
+        <v>50.11</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>17</v>
+        <v>772</v>
       </c>
       <c r="I14" s="14" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="J14" s="12" t="n">
         <v>4</v>
@@ -1365,23 +1363,23 @@
         <v>3</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>3</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P14" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q14" s="11" t="inlineStr">
         <is>
-          <t>Founded 2022; CES 2025 debut; Series A1 funded (Beijing AI Industry Investment Fund). Privacy=3: local offline AI for daily use; photo uploads encrypted on-device before cloud (ropetai.com). 39°C bionic warmth feature unique in this market (verified Amazon B0GTPZ4N4M). Stationary desktop companion — no locomotion (Movement=1). Brand Reliability=3: legitimate but newer; 30-day returns per manufacturer. Review strength=3: growing — recommend re-check as product matures. Review Strength=2: 17 reviews, 4.3★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=3, Familiar Form=2, Safety=4, Calmness=avg(Sound=3, Behavioral Realism=2)=2.5. Raw average of 4 sub-criteria=2.88, rounded=3, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>Hasbro 2023 'Hey Furby' — 25th anniversary edition. No app, no WiFi, no Bluetooth confirmed (Official Furby Wiki; IEEE Spectrum). 4x AA batteries. 5 voice-activated modes, 600+ pre-programmed reactions. Sound Level Control=2: no volume adjustment available (documented consumer complaint); only shutdown or mode switching. Brand=5: Hasbro, globally established, 58M+ units sold over 25 years. Review Strength=5: massive lifetime Amazon review volume. Dementia=2: loud/unpredictable, fantastical non-animal appearance — not recommended for memory care. Privacy=5: confirmed no wireless connectivity in 2023 model. IMPORTANT: DJ Furby (2025) is a different model from the Furby 2023 originally scored — elongated 'long oddbody' form factor with DJ/music theme (per Official Furby Wiki). Core feature scores carried over from 2023 Furby as closest available data; verify DJ-specific features (music modes, controls, form factor) before publishing. Review Strength=4: 772 reviews, 4.8★ (repo data, 2026-06-22). Visual contrast likely higher than regular Furby due to distinctive elongated DJ styling. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=4, Familiar Form=3, Safety=5, Calmness=avg(Sound=3, Behavioral Realism=3)=3.0. Raw average of 4 sub-criteria=3.75, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (was 2). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1391,35 +1389,35 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Wuffy</t>
+          <t>Ropet</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Wuffy Robot Puppy</t>
+          <t>KAMOMO</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Budget Friendly</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Robot</t>
         </is>
       </c>
       <c r="F15" s="8" t="n">
-        <v>25.99</v>
+        <v>349</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="J15" s="8" t="n">
         <v>4</v>
@@ -1428,14 +1426,14 @@
         <v>3</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M15" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="N15" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="N15" s="8" t="n">
-        <v>3</v>
-      </c>
       <c r="O15" s="8" t="n">
         <v>4</v>
       </c>
@@ -1444,7 +1442,7 @@
       </c>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>WARNING — LOW CONFIDENCE ACROSS ALL SCORES. No verified independent reviews found; all scores based on wuffyrobot.com marketing claims only. Review Strength=1: no verifiable third-party reviews identified. Brand Reliability=2: new/unverifiable brand, no established track record. Return/Gift Suitability=2: return policy unclear from DTC site. Recommend independent verification of product claims before featuring on site. Compare against Puppy Milow profile for scam-risk indicators. Review Strength=2: 80 reviews but only 3★ (repo data, 2026-06-22). Low rating confirms earlier caution flag about product quality/marketing claims. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=3, Familiar Form=3, Safety=4, Calmness=avg(Sound=2, Behavioral Realism=2)=2.0. Raw average of 4 sub-criteria=3.0, rounded=3, Evidence Tier D cap=3 -&gt; Final=3 (was 2). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>Founded 2022; CES 2025 debut; Series A1 funded (Beijing AI Industry Investment Fund). Privacy=3: local offline AI for daily use; photo uploads encrypted on-device before cloud (ropetai.com). 39°C bionic warmth feature unique in this market (verified Amazon B0GTPZ4N4M). Stationary desktop companion — no locomotion (Movement=1). Brand Reliability=3: legitimate but newer; 30-day returns per manufacturer. Review strength=3: growing — recommend re-check as product matures. Review Strength=2: 17 reviews, 4.3★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=3, Familiar Form=2, Safety=4, Calmness=avg(Sound=3, Behavioral Realism=2)=2.5. Raw average of 4 sub-criteria=2.88, rounded=3, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1452,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Ruko</t>
+          <t>Wuffy</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>18011 Smart Robot Dog</t>
+          <t>Wuffy Robot Puppy</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
@@ -1473,16 +1471,16 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>69.98999999999999</v>
+        <v>25.99</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>283</v>
-      </c>
-      <c r="I16" s="16" t="n">
-        <v>2.85</v>
+        <v>80</v>
+      </c>
+      <c r="I16" s="14" t="n">
+        <v>3.1</v>
       </c>
       <c r="J16" s="12" t="n">
         <v>4</v>
@@ -1491,7 +1489,7 @@
         <v>3</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>2</v>
@@ -1500,14 +1498,14 @@
         <v>3</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>3</v>
       </c>
       <c r="Q16" s="11" t="inlineStr">
         <is>
-          <t>Children's programmable toy robot dog with remote/gesture control. No WiFi or app required (infrared remote — Privacy=5). Hard plastic ABS shell, LED facial expressions, walks/spins/dances. 30-day returns, 90-day warranty per Amazon listing (B0FLXCXPHD). Sound Level Control=2: no volume adjustment noted; on/off states only. Dementia=1: remote-controlled, LED face, not a calming companion product. Not recommended for senior care use cases. Review Strength=3: 283 reviews, 4.4★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=3, Familiar Form=3, Safety=3, Calmness=avg(Sound=2, Behavioral Realism=2)=2.0. Raw average of 4 sub-criteria=2.75, rounded=3, Evidence Tier D cap=3 -&gt; Final=3 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>WARNING — LOW CONFIDENCE ACROSS ALL SCORES. No verified independent reviews found; all scores based on wuffyrobot.com marketing claims only. Review Strength=1: no verifiable third-party reviews identified. Brand Reliability=2: new/unverifiable brand, no established track record. Return/Gift Suitability=2: return policy unclear from DTC site. Recommend independent verification of product claims before featuring on site. Compare against Puppy Milow profile for scam-risk indicators. Review Strength=2: 80 reviews but only 3★ (repo data, 2026-06-22). Low rating confirms earlier caution flag about product quality/marketing claims. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=3, Familiar Form=3, Safety=4, Calmness=avg(Sound=2, Behavioral Realism=2)=2.0. Raw average of 4 sub-criteria=3.0, rounded=3, Evidence Tier D cap=3 -&gt; Final=3 (was 2). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1517,17 +1515,17 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Loona</t>
+          <t>Ruko</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Robot Pet Dog</t>
+          <t>18011 Smart Robot Dog</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>Budget Friendly</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -1536,41 +1534,41 @@
         </is>
       </c>
       <c r="F17" s="8" t="n">
-        <v>499</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>1199</v>
-      </c>
-      <c r="I17" s="17" t="n">
-        <v>1.95</v>
+        <v>283</v>
+      </c>
+      <c r="I17" s="16" t="n">
+        <v>2.85</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K17" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L17" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="L17" s="8" t="n">
-        <v>3</v>
-      </c>
       <c r="M17" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N17" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O17" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P17" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q17" s="7" t="inlineStr">
         <is>
-          <t>KEYi Tech Loona. Rubric anchor product: Control Accessibility=1 (worst) and Customization Options=5 (best). ChatGPT-4o integration. Camera, WiFi, app, account all required. Camera=yes, Internet Access=yes per Product Matrix. Voice=4: excellent AI voice response but conversational not animal-mimicry. Not recommended for seniors or dementia care. Review Strength=4: 1,199 reviews, 4.2★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=1, Familiar Form=2, Safety=2, Calmness=avg(Sound=3, Behavioral Realism=2)=2.5. Raw average of 4 sub-criteria=1.88, rounded=2, Evidence Tier D cap=3 -&gt; Final=2 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>Children's programmable toy robot dog with remote/gesture control. No WiFi or app required (infrared remote — Privacy=5). Hard plastic ABS shell, LED facial expressions, walks/spins/dances. 30-day returns, 90-day warranty per Amazon listing (B0FLXCXPHD). Sound Level Control=2: no volume adjustment noted; on/off states only. Dementia=1: remote-controlled, LED face, not a calming companion product. Not recommended for senior care use cases. Review Strength=3: 283 reviews, 4.4★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=3, Familiar Form=3, Safety=3, Calmness=avg(Sound=2, Behavioral Realism=2)=2.0. Raw average of 4 sub-criteria=2.75, rounded=3, Evidence Tier D cap=3 -&gt; Final=3 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1580,35 +1578,35 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Enabot</t>
+          <t>Loona</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>ROLA Mini Pet Monitor</t>
+          <t>Robot Pet Dog</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Best Value</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Robot</t>
+          <t>Dog</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>139</v>
+        <v>499</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>73</v>
-      </c>
-      <c r="I18" s="16" t="n">
-        <v>1.75</v>
+        <v>1199</v>
+      </c>
+      <c r="I18" s="17" t="n">
+        <v>1.95</v>
       </c>
       <c r="J18" s="12" t="n">
         <v>1</v>
@@ -1617,23 +1615,23 @@
         <v>2</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>3</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O18" s="12" t="n">
         <v>2</v>
       </c>
       <c r="P18" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="11" t="inlineStr">
         <is>
-          <t>Camera=yes, Internet Access=yes per Product Matrix. Hard-shell rolling security camera robot; not a companion pet. Scores are category-level; minor spec differences between models noted. Review strength and Value estimated — recommend manual Amazon verification. ROLA Mini is the most compact Enabot; Size=5. Charging=4 (dock, but smaller form factor). Product renamed to 'ROLA Mini Pet Monitor'. Review Strength=3: 73 reviews, 5★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=2, Familiar Form=1, Safety=2, Calmness=avg(Sound=3, Behavioral Realism=1)=2.0. Raw average of 4 sub-criteria=1.75, rounded=2, Evidence Tier D cap=3 -&gt; Final=2 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>KEYi Tech Loona. Rubric anchor product: Control Accessibility=1 (worst) and Customization Options=5 (best). ChatGPT-4o integration. Camera, WiFi, app, account all required. Camera=yes, Internet Access=yes per Product Matrix. Voice=4: excellent AI voice response but conversational not animal-mimicry. Not recommended for seniors or dementia care. Review Strength=4: 1,199 reviews, 4.2★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=1, Familiar Form=2, Safety=2, Calmness=avg(Sound=3, Behavioral Realism=2)=2.5. Raw average of 4 sub-criteria=1.88, rounded=2, Evidence Tier D cap=3 -&gt; Final=2 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1648,12 +1646,12 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>EBO Air 2 Plus FamilyBot</t>
+          <t>ROLA Mini Pet Monitor</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>Best Value</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -1662,15 +1660,15 @@
         </is>
       </c>
       <c r="F19" s="8" t="n">
-        <v>359</v>
+        <v>139</v>
       </c>
       <c r="G19" s="8" t="n">
         <v>5</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>42</v>
-      </c>
-      <c r="I19" s="17" t="n">
+        <v>73</v>
+      </c>
+      <c r="I19" s="16" t="n">
         <v>1.75</v>
       </c>
       <c r="J19" s="8" t="n">
@@ -1695,6 +1693,69 @@
         <v>2</v>
       </c>
       <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>Camera=yes, Internet Access=yes per Product Matrix. Hard-shell rolling security camera robot; not a companion pet. Scores are category-level; minor spec differences between models noted. Review strength and Value estimated — recommend manual Amazon verification. ROLA Mini is the most compact Enabot; Size=5. Charging=4 (dock, but smaller form factor). Product renamed to 'ROLA Mini Pet Monitor'. Review Strength=3: 73 reviews, 5★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=2, Familiar Form=1, Safety=2, Calmness=avg(Sound=3, Behavioral Realism=1)=2.0. Raw average of 4 sub-criteria=1.75, rounded=2, Evidence Tier D cap=3 -&gt; Final=2 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1">
+      <c r="A20" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Enabot</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>EBO Air 2 Plus FamilyBot</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>Robot</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>359</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="I20" s="17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="J20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="N20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="P20" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q20" s="11" t="inlineStr">
         <is>
           <t>Camera=yes, Internet Access=yes per Product Matrix. Hard-shell rolling security camera robot; not a companion pet. Scores are category-level; minor spec differences between models noted. Review strength and Value estimated — recommend manual Amazon verification. Air 2 Plus has AI chat mode — highest AI tier in Enabot lineup per manufacturer. Product renamed to 'EBO Air 2 Plus FamilyBot'. Review Strength=3: 42 reviews, 5★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=2, Familiar Form=1, Safety=2, Calmness=avg(Sound=3, Behavioral Realism=1)=2.0. Raw average of 4 sub-criteria=1.75, rounded=2, Evidence Tier D cap=3 -&gt; Final=2 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
@@ -1716,7 +1777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1976,7 +2037,7 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Grey Tabby Cat</t>
+          <t>Original Siamese Cat</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -1993,16 +2054,16 @@
         <v>3.8</v>
       </c>
       <c r="F8" s="20" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="G8" s="20" t="inlineStr">
         <is>
-          <t>Original Black and White Shorthair Cat</t>
+          <t>Grey Tabby Cat</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
         <is>
-          <t>score=3.80 rating=4.3</t>
+          <t>score=3.80 rating=4.1</t>
         </is>
       </c>
     </row>
@@ -2014,7 +2075,7 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>Original Siamese Cat</t>
+          <t>Original Plush White Cat</t>
         </is>
       </c>
       <c r="C9" s="19" t="inlineStr">
@@ -2031,16 +2092,16 @@
         <v>3.8</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G9" s="19" t="inlineStr">
         <is>
-          <t>Original Black and White Shorthair Cat</t>
+          <t>Grey Tabby Cat</t>
         </is>
       </c>
       <c r="H9" s="19" t="inlineStr">
         <is>
-          <t>score=3.80 rating=4.1</t>
+          <t>score=3.80 rating=4</t>
         </is>
       </c>
     </row>
@@ -2052,24 +2113,24 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Original Plush White Cat</t>
+          <t>Original Beagle</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>Budget Friendly</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Cat</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E10" s="20" t="n">
         <v>3.8</v>
       </c>
       <c r="F10" s="20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G10" s="20" t="inlineStr">
         <is>
@@ -2078,7 +2139,7 @@
       </c>
       <c r="H10" s="20" t="inlineStr">
         <is>
-          <t>score=3.80 rating=4</t>
+          <t>score=3.80 rating=0</t>
         </is>
       </c>
     </row>
@@ -2090,33 +2151,33 @@
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>Original Chocolate Lab</t>
+          <t>Original Shih Tzu</t>
         </is>
       </c>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t>Budget Friendly</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E11" s="19" t="n">
         <v>3.8</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="G11" s="19" t="inlineStr">
         <is>
-          <t>Original Beagle</t>
+          <t>Original Black and White Shorthair Cat</t>
         </is>
       </c>
       <c r="H11" s="19" t="inlineStr">
         <is>
-          <t>score=3.80 rating=4.3</t>
+          <t>score=3.80 rating=0</t>
         </is>
       </c>
     </row>
@@ -2149,7 +2210,7 @@
       </c>
       <c r="G12" s="20" t="inlineStr">
         <is>
-          <t>Original Beagle</t>
+          <t>Original Chocolate Lab</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -2161,38 +2222,38 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
         <is>
-          <t>Perfect Petzzz</t>
+          <t>Enabot</t>
         </is>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>Original Shih Tzu</t>
+          <t>EBO Air 2 FamilyBot</t>
         </is>
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
-          <t>Budget Friendly</t>
+          <t>Best Value</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Robot</t>
         </is>
       </c>
       <c r="E13" s="19" t="n">
-        <v>3.8</v>
+        <v>1.75</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="G13" s="19" t="inlineStr">
         <is>
-          <t>Original Beagle</t>
+          <t>ROLA Mini Pet Monitor</t>
         </is>
       </c>
       <c r="H13" s="19" t="inlineStr">
         <is>
-          <t>score=3.80 rating=4.2</t>
+          <t>score=1.75 rating=4.5</t>
         </is>
       </c>
     </row>
@@ -2204,12 +2265,12 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>EBO Air 2 FamilyBot</t>
+          <t>EBO Air 2S FamilyBot</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>Best Value</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -2221,16 +2282,16 @@
         <v>1.75</v>
       </c>
       <c r="F14" s="20" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G14" s="20" t="inlineStr">
         <is>
-          <t>ROLA Mini Pet Monitor</t>
+          <t>EBO Air 2 Plus FamilyBot</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
         <is>
-          <t>score=1.75 rating=4.5</t>
+          <t>score=1.75 rating=5</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2303,7 @@
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>EBO Air 2S FamilyBot</t>
+          <t>EBO X FamilyBot</t>
         </is>
       </c>
       <c r="C15" s="19" t="inlineStr">
@@ -2259,7 +2320,7 @@
         <v>1.75</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="G15" s="19" t="inlineStr">
         <is>
@@ -2267,44 +2328,6 @@
         </is>
       </c>
       <c r="H15" s="19" t="inlineStr">
-        <is>
-          <t>score=1.75 rating=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>Enabot</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>EBO X FamilyBot</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>Premium</t>
-        </is>
-      </c>
-      <c r="D16" s="20" t="inlineStr">
-        <is>
-          <t>Robot</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="F16" s="20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G16" s="20" t="inlineStr">
-        <is>
-          <t>EBO Air 2 Plus FamilyBot</t>
-        </is>
-      </c>
-      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>score=1.75 rating=4.5</t>
         </is>

--- a/Documentation/Best For Lists/Best for Seniors with Dementia List.xlsx
+++ b/Documentation/Best For Lists/Best for Seniors with Dementia List.xlsx
@@ -620,7 +620,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-07  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
+          <t>Generated: 2026-07-08  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
         </is>
       </c>
     </row>

--- a/Documentation/Best For Lists/Best for Seniors with Dementia List.xlsx
+++ b/Documentation/Best For Lists/Best for Seniors with Dementia List.xlsx
@@ -620,7 +620,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-08  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
+          <t>Generated: 2026-07-11  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>Robot</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
